--- a/data/Verzasca/investment_decision/Gerra_SFH_2005-2014_investment_decision.xlsx
+++ b/data/Verzasca/investment_decision/Gerra_SFH_2005-2014_investment_decision.xlsx
@@ -17,8 +17,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -58,12 +58,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -460,24 +461,24 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>scen_cp_dr_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_dr_candidate_unit</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>scen_cp_cu_invested_available_unit</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_cu_candidate_unit</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_dr_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_dr_candidate_unit</t>
-        </is>
-      </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>scen_all_invested_available_unit</t>
@@ -490,11 +491,11 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B2" t="n">
-        <v>11.47949539224499</v>
+        <v>6.184112806388714</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -508,30 +509,30 @@
         <v>3005.550681121943</v>
       </c>
       <c r="F2" t="n">
-        <v>12.17817898800462</v>
+        <v>6.737856415297307</v>
       </c>
       <c r="G2" t="n">
         <v>3005.550681121943</v>
       </c>
       <c r="H2" t="n">
-        <v>12.08203749186567</v>
+        <v>5.720369418356813</v>
       </c>
       <c r="I2" t="n">
         <v>3005.550681121943</v>
       </c>
       <c r="J2" t="n">
-        <v>15.88964260878524</v>
+        <v>6.737856415297308</v>
       </c>
       <c r="K2" t="n">
         <v>3005.550681121943</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B3" t="n">
-        <v>14.84262344592917</v>
+        <v>10.00293463232333</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -545,30 +546,30 @@
         <v>3005.550681121943</v>
       </c>
       <c r="F3" t="n">
-        <v>17.43960864889374</v>
+        <v>10.61834729644069</v>
       </c>
       <c r="G3" t="n">
         <v>3005.550681121943</v>
       </c>
       <c r="H3" t="n">
-        <v>16.28460928296453</v>
+        <v>9.997956040728123</v>
       </c>
       <c r="I3" t="n">
         <v>3005.550681121943</v>
       </c>
       <c r="J3" t="n">
-        <v>16.41373935719814</v>
+        <v>10.61834729644069</v>
       </c>
       <c r="K3" t="n">
         <v>3005.550681121943</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B4" t="n">
-        <v>14.84262344592917</v>
+        <v>17.10130899243535</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -582,30 +583,30 @@
         <v>3005.550681121943</v>
       </c>
       <c r="F4" t="n">
-        <v>17.43960864889374</v>
+        <v>17.18557179893829</v>
       </c>
       <c r="G4" t="n">
         <v>3005.550681121943</v>
       </c>
       <c r="H4" t="n">
-        <v>16.28460928296453</v>
+        <v>17.21949227283848</v>
       </c>
       <c r="I4" t="n">
         <v>3005.550681121943</v>
       </c>
       <c r="J4" t="n">
-        <v>16.41373935719814</v>
+        <v>17.21949227283848</v>
       </c>
       <c r="K4" t="n">
         <v>3005.550681121943</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B5" t="n">
-        <v>19.06852353429043</v>
+        <v>17.92210330467309</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -619,30 +620,30 @@
         <v>3005.550681121943</v>
       </c>
       <c r="F5" t="n">
-        <v>17.43960864889374</v>
+        <v>17.92210330467305</v>
       </c>
       <c r="G5" t="n">
         <v>3005.550681121943</v>
       </c>
       <c r="H5" t="n">
-        <v>17.42025133425834</v>
+        <v>17.92210330467308</v>
       </c>
       <c r="I5" t="n">
         <v>3005.550681121943</v>
       </c>
       <c r="J5" t="n">
-        <v>17.17494390944518</v>
+        <v>17.92210330467307</v>
       </c>
       <c r="K5" t="n">
         <v>3005.550681121943</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B6" t="n">
-        <v>19.06852353429043</v>
+        <v>17.92210330467309</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -656,26 +657,26 @@
         <v>3005.550681121943</v>
       </c>
       <c r="F6" t="n">
-        <v>17.43960864889374</v>
+        <v>17.92210330467305</v>
       </c>
       <c r="G6" t="n">
         <v>3005.550681121943</v>
       </c>
       <c r="H6" t="n">
-        <v>17.42025133425834</v>
+        <v>17.92210330467308</v>
       </c>
       <c r="I6" t="n">
         <v>3005.550681121943</v>
       </c>
       <c r="J6" t="n">
-        <v>17.17494390944518</v>
+        <v>17.92210330467308</v>
       </c>
       <c r="K6" t="n">
         <v>3005.550681121943</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B7" t="n">
@@ -683,36 +684,36 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Gerra_b_SFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Gerra_b_SFH_2005-2014</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E7" t="n">
-        <v>4.508326021682915</v>
+        <v>5.882812584269663</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>2.567309032797168</v>
+        <v>5.882812584269663</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>4.508326021682915</v>
+        <v>3.350023448439639</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>2.567309032797168</v>
+        <v>3.350023448439639</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B8" t="n">
@@ -720,36 +721,36 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Gerra_b_SFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Gerra_b_SFH_2005-2014</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E8" t="n">
-        <v>4.508326021682915</v>
+        <v>5.882812584269663</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>3.125144597205514</v>
+        <v>5.882812584269663</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>4.508326021682915</v>
+        <v>4.07793045038924</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>3.125144597205514</v>
+        <v>4.07793045038924</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B9" t="n">
@@ -757,36 +758,36 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Gerra_b_SFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Gerra_b_SFH_2005-2014</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E9" t="n">
-        <v>4.508326021682915</v>
+        <v>5.882812584269663</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>3.353650867251972</v>
+        <v>5.882812584269663</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>4.508326021682915</v>
+        <v>4.376103110163306</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>3.353650867251972</v>
+        <v>4.376103110163306</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B10" t="n">
@@ -794,36 +795,36 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Gerra_b_SFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Gerra_b_SFH_2005-2014</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E10" t="n">
-        <v>4.508326021682915</v>
+        <v>5.882812584269663</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>3.475797925734497</v>
+        <v>5.882812584269663</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>4.508326021682915</v>
+        <v>4.535490042101358</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>3.475797925734497</v>
+        <v>4.535490042101358</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B11" t="n">
@@ -831,40 +832,40 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Gerra_b_SFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Gerra_b_SFH_2005-2014</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E11" t="n">
-        <v>4.508326021682915</v>
+        <v>5.882812584269663</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>3.552124087040821</v>
+        <v>5.882812584269663</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>4.508326021682915</v>
+        <v>4.635086322424099</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>3.552124087040821</v>
+        <v>4.635086322424099</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B12" t="n">
-        <v>0.0009503461270588236</v>
+        <v>0.0008711506164705882</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -878,30 +879,30 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0009503461270588236</v>
+        <v>0.0008711506164705882</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0009503461270588236</v>
+        <v>0.0008315528611764705</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0009503461270588236</v>
+        <v>0.0008315528611764705</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B13" t="n">
-        <v>0.0009503461270588236</v>
+        <v>0.0008711506164705882</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -915,30 +916,30 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0009503461270588236</v>
+        <v>0.0008711506164705881</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0009503461270588236</v>
+        <v>0.0008315528611764704</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0009503461270588236</v>
+        <v>0.0008315528611764704</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B14" t="n">
-        <v>0.0009503461270588236</v>
+        <v>0.0008711506164705881</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -952,30 +953,30 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0009503461270588236</v>
+        <v>0.0008711506164705882</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0009503461270588236</v>
+        <v>0.0008315528611764705</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0009503461270588236</v>
+        <v>0.0008315528611764705</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B15" t="n">
-        <v>0.0009503461270588236</v>
+        <v>0.0008711506164705882</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -989,30 +990,30 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0009503461270588236</v>
+        <v>0.0008711506164705881</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0009503461270588236</v>
+        <v>0.0008711506164705882</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0009503461270588236</v>
+        <v>0.0008711506164705881</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B16" t="n">
-        <v>0.0009503461270588236</v>
+        <v>0.0008711506164705882</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1026,30 +1027,30 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0009503461270588236</v>
+        <v>0.0008711506164705882</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0009503461270588236</v>
+        <v>0.0008711506164705881</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0009503461270588236</v>
+        <v>0.0008711506164705881</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>0.2178426981803528</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1063,30 +1064,30 @@
         <v>0.706819932</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>0.2165273595919579</v>
       </c>
       <c r="G17" t="n">
         <v>0.706819932</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>0.1689778306362703</v>
       </c>
       <c r="I17" t="n">
         <v>0.706819932</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>0.1609402491786152</v>
       </c>
       <c r="K17" t="n">
         <v>0.706819932</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B18" t="n">
-        <v>0.3576172275</v>
+        <v>0.311841650710277</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1100,30 +1101,30 @@
         <v>0.706819932</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3576172275</v>
+        <v>0.3137002551312018</v>
       </c>
       <c r="G18" t="n">
         <v>0.706819932</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3576172275</v>
+        <v>0.2629767831661944</v>
       </c>
       <c r="I18" t="n">
         <v>0.706819932</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3576172275</v>
+        <v>0.2661217866786153</v>
       </c>
       <c r="K18" t="n">
         <v>0.706819932</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B19" t="n">
-        <v>0.5469439949999998</v>
+        <v>0.5011253917533017</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1137,30 +1138,30 @@
         <v>0.706819932</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5469439949999998</v>
+        <v>0.5030270226312014</v>
       </c>
       <c r="G19" t="n">
         <v>0.706819932</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5469439949999998</v>
+        <v>0.4480150337139279</v>
       </c>
       <c r="I19" t="n">
         <v>0.706819932</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5469439949999998</v>
+        <v>0.4554485541786151</v>
       </c>
       <c r="K19" t="n">
         <v>0.706819932</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B20" t="n">
-        <v>0.5469439949999999</v>
+        <v>0.3645183545343685</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1174,30 +1175,30 @@
         <v>0.706819932</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5469439949999998</v>
+        <v>0.3653242612568037</v>
       </c>
       <c r="G20" t="n">
         <v>0.706819932</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5469439949999999</v>
+        <v>0.3409215897147125</v>
       </c>
       <c r="I20" t="n">
         <v>0.706819932</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5469439949999998</v>
+        <v>0.3390738099296557</v>
       </c>
       <c r="K20" t="n">
         <v>0.706819932</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B21" t="n">
-        <v>0.1893267674999999</v>
+        <v>0.2705194020044444</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1211,26 +1212,26 @@
         <v>0.706819932</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1893267674999998</v>
+        <v>0.2681513657175599</v>
       </c>
       <c r="G21" t="n">
         <v>0.706819932</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1893267674999999</v>
+        <v>0.2469226371847884</v>
       </c>
       <c r="I21" t="n">
         <v>0.706819932</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1893267674999998</v>
+        <v>0.2338922724296556</v>
       </c>
       <c r="K21" t="n">
         <v>0.706819932</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B22" t="n">
@@ -1267,7 +1268,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B23" t="n">
@@ -1304,7 +1305,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B24" t="n">
@@ -1341,7 +1342,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B25" t="n">
@@ -1378,7 +1379,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B26" t="n">
@@ -1415,11 +1416,11 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>0.0458186032466981</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1433,30 +1434,30 @@
         <v>0.706819932</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>0.04391697236879855</v>
       </c>
       <c r="G27" t="n">
         <v>0.706819932</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>0.098928961286072</v>
       </c>
       <c r="I27" t="n">
         <v>0.706819932</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>0.09149544082138471</v>
       </c>
       <c r="K27" t="n">
         <v>0.706819932</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>0.0458186032466981</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1470,30 +1471,30 @@
         <v>0.706819932</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>0.04391697236879855</v>
       </c>
       <c r="G28" t="n">
         <v>0.706819932</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>0.098928961286072</v>
       </c>
       <c r="I28" t="n">
         <v>0.706819932</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>0.09149544082138471</v>
       </c>
       <c r="K28" t="n">
         <v>0.706819932</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>0.0458186032466981</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1507,30 +1508,30 @@
         <v>0.706819932</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>0.04391697236879855</v>
       </c>
       <c r="G29" t="n">
         <v>0.706819932</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>0.098928961286072</v>
       </c>
       <c r="I29" t="n">
         <v>0.706819932</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>0.09149544082138471</v>
       </c>
       <c r="K29" t="n">
         <v>0.706819932</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>0.002952595495555598</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1544,30 +1545,30 @@
         <v>0.706819932</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>0.002146688773120486</v>
       </c>
       <c r="G30" t="n">
         <v>0.706819932</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>0.02654936031521158</v>
       </c>
       <c r="I30" t="n">
         <v>0.706819932</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.02839714010026846</v>
       </c>
       <c r="K30" t="n">
         <v>0.706819932</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>0.002952595495555598</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1581,26 +1582,26 @@
         <v>0.706819932</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>0.002146688773120486</v>
       </c>
       <c r="G31" t="n">
         <v>0.706819932</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>0.02654936031521158</v>
       </c>
       <c r="I31" t="n">
         <v>0.706819932</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>0.02839714010026846</v>
       </c>
       <c r="K31" t="n">
         <v>0.706819932</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B32" t="n">
@@ -1637,7 +1638,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B33" t="n">
@@ -1674,7 +1675,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B34" t="n">
@@ -1711,7 +1712,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B35" t="n">
@@ -1748,7 +1749,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B36" t="n">
@@ -1785,7 +1786,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B37" t="n">
@@ -1822,7 +1823,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B38" t="n">
@@ -1859,7 +1860,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B39" t="n">
@@ -1896,7 +1897,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B40" t="n">
@@ -1933,7 +1934,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B41" t="n">
@@ -1970,7 +1971,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B42" t="n">
@@ -1991,13 +1992,13 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
+        <v>7.267938148175781</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
         <v>4.214132002604725</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" t="n">
-        <v>7.267938148175781</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2007,7 +2008,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B43" t="n">
@@ -2028,13 +2029,13 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
+        <v>7.267938148175781</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
         <v>5.123702379349046</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="n">
-        <v>7.267938148175781</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2044,7 +2045,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B44" t="n">
@@ -2065,13 +2066,13 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
+        <v>7.267938148175781</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
         <v>5.498288922823106</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="n">
-        <v>7.267938148175781</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2081,7 +2082,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B45" t="n">
@@ -2102,13 +2103,13 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
+        <v>7.267938148175781</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
         <v>5.701345405610331</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" t="n">
-        <v>7.267938148175781</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -2118,7 +2119,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B46" t="n">
@@ -2139,13 +2140,13 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
+        <v>7.267938148175781</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
         <v>5.830388305162501</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" t="n">
-        <v>7.267938148175781</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -2155,7 +2156,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B47" t="n">
@@ -2192,7 +2193,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B48" t="n">
@@ -2229,7 +2230,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B49" t="n">
@@ -2266,7 +2267,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B50" t="n">
@@ -2303,7 +2304,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B51" t="n">
@@ -2340,7 +2341,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B52" t="n">
@@ -2358,30 +2359,30 @@
         <v>5.288361907086144</v>
       </c>
       <c r="F52" t="n">
-        <v>0.711967573175743</v>
+        <v>0</v>
       </c>
       <c r="G52" t="n">
+        <v>5.288361907086144</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
         <v>1.659249662533367</v>
       </c>
-      <c r="H52" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" t="n">
-        <v>5.288361907086144</v>
-      </c>
       <c r="J52" t="n">
-        <v>0.6300970521291116</v>
+        <v>0</v>
       </c>
       <c r="K52" t="n">
         <v>1.659249662533367</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B53" t="n">
-        <v>0.7053439390113302</v>
+        <v>0.8350018829661559</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2395,30 +2396,30 @@
         <v>5.288361907086144</v>
       </c>
       <c r="F53" t="n">
-        <v>1.322382208823852</v>
+        <v>0.8316824550645453</v>
       </c>
       <c r="G53" t="n">
+        <v>5.288361907086144</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.8081515105665896</v>
+      </c>
+      <c r="I53" t="n">
         <v>2.182714966537852</v>
       </c>
-      <c r="H53" t="n">
-        <v>0.5496414506424102</v>
-      </c>
-      <c r="I53" t="n">
-        <v>5.288361907086144</v>
-      </c>
       <c r="J53" t="n">
-        <v>1.170209575467635</v>
+        <v>0.8316824550645453</v>
       </c>
       <c r="K53" t="n">
         <v>2.182714966537852</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B54" t="n">
-        <v>0.7053439390113302</v>
+        <v>1.09581788377796</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2432,30 +2433,30 @@
         <v>5.288361907086144</v>
       </c>
       <c r="F54" t="n">
-        <v>1.322382208823852</v>
+        <v>1.038553142343701</v>
       </c>
       <c r="G54" t="n">
+        <v>5.288361907086144</v>
+      </c>
+      <c r="H54" t="n">
+        <v>1.032413106376578</v>
+      </c>
+      <c r="I54" t="n">
         <v>2.41599686818329</v>
       </c>
-      <c r="H54" t="n">
-        <v>0.6317880472453984</v>
-      </c>
-      <c r="I54" t="n">
-        <v>5.288361907086144</v>
-      </c>
       <c r="J54" t="n">
-        <v>1.203217887876523</v>
+        <v>1.017431715565846</v>
       </c>
       <c r="K54" t="n">
         <v>2.41599686818329</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B55" t="n">
-        <v>1.392258792494107</v>
+        <v>1.377975396441193</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2469,30 +2470,30 @@
         <v>5.288361907086144</v>
       </c>
       <c r="F55" t="n">
-        <v>1.37523623054098</v>
+        <v>1.372452063187834</v>
       </c>
       <c r="G55" t="n">
+        <v>5.288361907086144</v>
+      </c>
+      <c r="H55" t="n">
+        <v>1.375975906530014</v>
+      </c>
+      <c r="I55" t="n">
         <v>2.541894044895371</v>
       </c>
-      <c r="H55" t="n">
-        <v>1.366653284903785</v>
-      </c>
-      <c r="I55" t="n">
-        <v>5.288361907086144</v>
-      </c>
       <c r="J55" t="n">
-        <v>1.346242332512486</v>
+        <v>1.372452063187834</v>
       </c>
       <c r="K55" t="n">
         <v>2.541894044895371</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B56" t="n">
-        <v>1.378113032472308</v>
+        <v>1.377975396441194</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2506,26 +2507,26 @@
         <v>5.288361907086144</v>
       </c>
       <c r="F56" t="n">
-        <v>1.366226285316239</v>
+        <v>1.270160937925503</v>
       </c>
       <c r="G56" t="n">
+        <v>5.288361907086144</v>
+      </c>
+      <c r="H56" t="n">
+        <v>1.375975906530014</v>
+      </c>
+      <c r="I56" t="n">
         <v>2.619611178262551</v>
       </c>
-      <c r="H56" t="n">
-        <v>1.284563018321822</v>
-      </c>
-      <c r="I56" t="n">
-        <v>5.288361907086144</v>
-      </c>
       <c r="J56" t="n">
-        <v>1.272699939549511</v>
+        <v>1.248862120012943</v>
       </c>
       <c r="K56" t="n">
         <v>2.619611178262551</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B57" t="n">
@@ -2546,13 +2547,13 @@
         <v>0</v>
       </c>
       <c r="G57" t="n">
+        <v>5.288361907086144</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
         <v>1.659249662533367</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" t="n">
-        <v>5.288361907086144</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -2562,7 +2563,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B58" t="n">
@@ -2583,13 +2584,13 @@
         <v>0</v>
       </c>
       <c r="G58" t="n">
+        <v>5.288361907086144</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
         <v>2.182714966537852</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" t="n">
-        <v>5.288361907086144</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -2599,7 +2600,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B59" t="n">
@@ -2620,13 +2621,13 @@
         <v>0</v>
       </c>
       <c r="G59" t="n">
+        <v>5.288361907086144</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
         <v>2.41599686818329</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" t="n">
-        <v>5.288361907086144</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -2636,7 +2637,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B60" t="n">
@@ -2657,13 +2658,13 @@
         <v>0</v>
       </c>
       <c r="G60" t="n">
+        <v>5.288361907086144</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
         <v>2.541894044895371</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" t="n">
-        <v>5.288361907086144</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -2673,7 +2674,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B61" t="n">
@@ -2694,13 +2695,13 @@
         <v>0</v>
       </c>
       <c r="G61" t="n">
+        <v>5.288361907086144</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="n">
         <v>2.619611178262551</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" t="n">
-        <v>5.288361907086144</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -2710,7 +2711,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -2747,11 +2748,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B63" t="n">
-        <v>0.07487030631832177</v>
+        <v>0</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -2765,30 +2766,30 @@
         <v>5.288361907086144</v>
       </c>
       <c r="F63" t="n">
-        <v>0.1056220051812907</v>
+        <v>0</v>
       </c>
       <c r="G63" t="n">
         <v>5.288361907086144</v>
       </c>
       <c r="H63" t="n">
-        <v>0.2120556534207415</v>
+        <v>0</v>
       </c>
       <c r="I63" t="n">
         <v>5.288361907086144</v>
       </c>
       <c r="J63" t="n">
-        <v>0.2824271777646111</v>
+        <v>0</v>
       </c>
       <c r="K63" t="n">
         <v>5.288361907086144</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B64" t="n">
-        <v>1.074870306318322</v>
+        <v>0.3456296876206472</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2802,30 +2803,30 @@
         <v>5.288361907086144</v>
       </c>
       <c r="F64" t="n">
-        <v>1.105622005181291</v>
+        <v>0.4293004894181436</v>
       </c>
       <c r="G64" t="n">
         <v>5.288361907086144</v>
       </c>
       <c r="H64" t="n">
-        <v>1.129909056817753</v>
+        <v>0.3823203652642019</v>
       </c>
       <c r="I64" t="n">
         <v>5.288361907086144</v>
       </c>
       <c r="J64" t="n">
-        <v>1.249418865355723</v>
+        <v>0.4524160665445921</v>
       </c>
       <c r="K64" t="n">
         <v>5.288361907086144</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B65" t="n">
-        <v>1.230693507256703</v>
+        <v>0.5600047680296373</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2839,30 +2840,30 @@
         <v>5.288361907086144</v>
       </c>
       <c r="F65" t="n">
-        <v>1.261344710869908</v>
+        <v>0.5655281012829969</v>
       </c>
       <c r="G65" t="n">
         <v>5.288361907086144</v>
       </c>
       <c r="H65" t="n">
-        <v>1.292657960435968</v>
+        <v>0.5620042579408164</v>
       </c>
       <c r="I65" t="n">
         <v>5.288361907086144</v>
       </c>
       <c r="J65" t="n">
-        <v>1.298179871237703</v>
+        <v>0.5655281012829965</v>
       </c>
       <c r="K65" t="n">
         <v>5.288361907086144</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B66" t="n">
-        <v>1.574386205143546</v>
+        <v>0.5600047680296371</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2876,26 +2877,26 @@
         <v>5.288361907086144</v>
       </c>
       <c r="F66" t="n">
-        <v>1.622204898301013</v>
+        <v>0.6678192265453273</v>
       </c>
       <c r="G66" t="n">
         <v>5.288361907086144</v>
       </c>
       <c r="H66" t="n">
-        <v>1.704295164882976</v>
+        <v>0.5620042579408165</v>
       </c>
       <c r="I66" t="n">
         <v>5.288361907086144</v>
       </c>
       <c r="J66" t="n">
-        <v>1.721569436849694</v>
+        <v>0.6891180444578874</v>
       </c>
       <c r="K66" t="n">
         <v>5.288361907086144</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B67" t="n">
@@ -2932,7 +2933,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B68" t="n">
@@ -2969,7 +2970,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B69" t="n">
@@ -3006,7 +3007,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B70" t="n">
@@ -3043,7 +3044,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B71" t="n">
@@ -3080,7 +3081,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="A72" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B72" t="n">
@@ -3101,7 +3102,7 @@
         <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>0.1636696806395379</v>
+        <v>5.288361907086144</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -3113,11 +3114,11 @@
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>0.1636696806395379</v>
+        <v>5.288361907086144</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B73" t="n">
@@ -3138,7 +3139,7 @@
         <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>0.2534837741719522</v>
+        <v>5.288361907086144</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -3150,11 +3151,11 @@
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>0.2534837741719522</v>
+        <v>5.288361907086144</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B74" t="n">
@@ -3175,7 +3176,7 @@
         <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>0.3126951513773169</v>
+        <v>5.288361907086144</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -3187,11 +3188,11 @@
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>0.3126951513773169</v>
+        <v>5.288361907086144</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B75" t="n">
@@ -3212,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>0.3558117151411356</v>
+        <v>5.288361907086144</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -3224,11 +3225,11 @@
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>0.3558117151411356</v>
+        <v>5.288361907086144</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B76" t="n">
@@ -3249,7 +3250,7 @@
         <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>0.3891872698118913</v>
+        <v>5.288361907086144</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -3261,15 +3262,15 @@
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>0.3891872698118913</v>
+        <v>5.288361907086144</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B77" t="n">
-        <v>0.9359564387232449</v>
+        <v>0.5159573823927091</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -3283,30 +3284,30 @@
         <v>5.288361907086144</v>
       </c>
       <c r="F77" t="n">
-        <v>0.2085767274057451</v>
+        <v>0.487557171680878</v>
       </c>
       <c r="G77" t="n">
-        <v>0.1636696806395379</v>
+        <v>5.288361907086144</v>
       </c>
       <c r="H77" t="n">
-        <v>0.9226650688786708</v>
+        <v>0.5426714821505363</v>
       </c>
       <c r="I77" t="n">
         <v>5.288361907086144</v>
       </c>
       <c r="J77" t="n">
-        <v>0.2085767274057451</v>
+        <v>0.487557171680878</v>
       </c>
       <c r="K77" t="n">
-        <v>0.1636696806395379</v>
+        <v>5.288361907086144</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B78" t="n">
-        <v>0.9359564387232449</v>
+        <v>0.5159573823927091</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -3320,30 +3321,30 @@
         <v>5.288361907086144</v>
       </c>
       <c r="F78" t="n">
-        <v>0.2308800317470648</v>
+        <v>0.487557171680878</v>
       </c>
       <c r="G78" t="n">
-        <v>0.2534837741719522</v>
+        <v>5.288361907086144</v>
       </c>
       <c r="H78" t="n">
-        <v>0.9226650688786708</v>
+        <v>0.5426714821505363</v>
       </c>
       <c r="I78" t="n">
         <v>5.288361907086144</v>
       </c>
       <c r="J78" t="n">
-        <v>0.2288769621897171</v>
+        <v>0.487557171680878</v>
       </c>
       <c r="K78" t="n">
-        <v>0.2534837741719522</v>
+        <v>5.288361907086144</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="A79" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B79" t="n">
-        <v>0.9359564387232449</v>
+        <v>0.5159573823927091</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -3357,26 +3358,26 @@
         <v>5.288361907086144</v>
       </c>
       <c r="F79" t="n">
-        <v>0.2308800317470648</v>
+        <v>0.487557171680878</v>
       </c>
       <c r="G79" t="n">
-        <v>0.3126951513773169</v>
+        <v>5.288361907086144</v>
       </c>
       <c r="H79" t="n">
-        <v>0.9226650688786709</v>
+        <v>0.5426714821505363</v>
       </c>
       <c r="I79" t="n">
         <v>5.288361907086144</v>
       </c>
       <c r="J79" t="n">
-        <v>0.2288769621897171</v>
+        <v>0.487557171680878</v>
       </c>
       <c r="K79" t="n">
-        <v>0.3126951513773169</v>
+        <v>5.288361907086144</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n">
+      <c r="A80" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B80" t="n">
@@ -3394,10 +3395,10 @@
         <v>5.288361907086144</v>
       </c>
       <c r="F80" t="n">
-        <v>0.02230330434131975</v>
+        <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>0.3558117151411356</v>
+        <v>5.288361907086144</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -3406,14 +3407,14 @@
         <v>5.288361907086144</v>
       </c>
       <c r="J80" t="n">
-        <v>0.02030023478397203</v>
+        <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>0.3558117151411356</v>
+        <v>5.288361907086144</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n">
+      <c r="A81" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B81" t="n">
@@ -3434,7 +3435,7 @@
         <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>0.3891872698118913</v>
+        <v>5.288361907086144</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -3446,11 +3447,11 @@
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>0.3891872698118913</v>
+        <v>5.288361907086144</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n">
+      <c r="A82" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B82" t="n">
@@ -3469,13 +3470,13 @@
         <v>0</v>
       </c>
       <c r="G82" t="n">
+        <v>1</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" t="n">
         <v>0.4293250562242569</v>
-      </c>
-      <c r="H82" t="n">
-        <v>0</v>
-      </c>
-      <c r="I82" t="n">
-        <v>1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -3485,7 +3486,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="n">
+      <c r="A83" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B83" t="n">
@@ -3504,13 +3505,13 @@
         <v>0</v>
       </c>
       <c r="G83" t="n">
+        <v>1</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" t="n">
         <v>0.5615523961267772</v>
-      </c>
-      <c r="H83" t="n">
-        <v>0</v>
-      </c>
-      <c r="I83" t="n">
-        <v>1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -3520,7 +3521,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n">
+      <c r="A84" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B84" t="n">
@@ -3539,13 +3540,13 @@
         <v>0</v>
       </c>
       <c r="G84" t="n">
+        <v>1</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" t="n">
         <v>0.624556919057325</v>
-      </c>
-      <c r="H84" t="n">
-        <v>0</v>
-      </c>
-      <c r="I84" t="n">
-        <v>1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -3555,7 +3556,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n">
+      <c r="A85" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B85" t="n">
@@ -3574,13 +3575,13 @@
         <v>0</v>
       </c>
       <c r="G85" t="n">
+        <v>1</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" t="n">
         <v>0.6622379613453093</v>
-      </c>
-      <c r="H85" t="n">
-        <v>0</v>
-      </c>
-      <c r="I85" t="n">
-        <v>1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -3590,7 +3591,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n">
+      <c r="A86" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B86" t="n">
@@ -3609,13 +3610,13 @@
         <v>0</v>
       </c>
       <c r="G86" t="n">
+        <v>1</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" t="n">
         <v>0.6881588528152967</v>
-      </c>
-      <c r="H86" t="n">
-        <v>0</v>
-      </c>
-      <c r="I86" t="n">
-        <v>1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -3625,7 +3626,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n">
+      <c r="A87" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B87" t="n">
@@ -3644,13 +3645,13 @@
         <v>0</v>
       </c>
       <c r="G87" t="n">
+        <v>1</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" t="n">
         <v>0.4293250562242569</v>
-      </c>
-      <c r="H87" t="n">
-        <v>0</v>
-      </c>
-      <c r="I87" t="n">
-        <v>1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -3660,7 +3661,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n">
+      <c r="A88" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B88" t="n">
@@ -3679,13 +3680,13 @@
         <v>0</v>
       </c>
       <c r="G88" t="n">
+        <v>1</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" t="n">
         <v>0.5615523961267772</v>
-      </c>
-      <c r="H88" t="n">
-        <v>0</v>
-      </c>
-      <c r="I88" t="n">
-        <v>1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -3695,7 +3696,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n">
+      <c r="A89" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B89" t="n">
@@ -3714,13 +3715,13 @@
         <v>0</v>
       </c>
       <c r="G89" t="n">
+        <v>1</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" t="n">
         <v>0.624556919057325</v>
-      </c>
-      <c r="H89" t="n">
-        <v>0</v>
-      </c>
-      <c r="I89" t="n">
-        <v>1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -3730,7 +3731,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n">
+      <c r="A90" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B90" t="n">
@@ -3749,13 +3750,13 @@
         <v>0</v>
       </c>
       <c r="G90" t="n">
+        <v>1</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" t="n">
         <v>0.6622379613453093</v>
-      </c>
-      <c r="H90" t="n">
-        <v>0</v>
-      </c>
-      <c r="I90" t="n">
-        <v>1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -3765,7 +3766,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n">
+      <c r="A91" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B91" t="n">
@@ -3784,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="G91" t="n">
+        <v>1</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" t="n">
         <v>0.6881588528152967</v>
-      </c>
-      <c r="H91" t="n">
-        <v>0</v>
-      </c>
-      <c r="I91" t="n">
-        <v>1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -3800,7 +3801,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n">
+      <c r="A92" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B92" t="n">
@@ -3819,13 +3820,13 @@
         <v>0</v>
       </c>
       <c r="G92" t="n">
+        <v>1</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" t="n">
         <v>0.4293250562242569</v>
-      </c>
-      <c r="H92" t="n">
-        <v>0</v>
-      </c>
-      <c r="I92" t="n">
-        <v>1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -3835,7 +3836,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n">
+      <c r="A93" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B93" t="n">
@@ -3854,13 +3855,13 @@
         <v>0</v>
       </c>
       <c r="G93" t="n">
+        <v>1</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" t="n">
         <v>0.5615523961267772</v>
-      </c>
-      <c r="H93" t="n">
-        <v>0</v>
-      </c>
-      <c r="I93" t="n">
-        <v>1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -3870,7 +3871,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n">
+      <c r="A94" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B94" t="n">
@@ -3889,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="G94" t="n">
+        <v>1</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" t="n">
         <v>0.624556919057325</v>
-      </c>
-      <c r="H94" t="n">
-        <v>0</v>
-      </c>
-      <c r="I94" t="n">
-        <v>1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -3905,7 +3906,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="n">
+      <c r="A95" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B95" t="n">
@@ -3924,13 +3925,13 @@
         <v>0</v>
       </c>
       <c r="G95" t="n">
+        <v>1</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" t="n">
         <v>0.6622379613453093</v>
-      </c>
-      <c r="H95" t="n">
-        <v>0</v>
-      </c>
-      <c r="I95" t="n">
-        <v>1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -3940,7 +3941,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n">
+      <c r="A96" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B96" t="n">
@@ -3959,13 +3960,13 @@
         <v>0</v>
       </c>
       <c r="G96" t="n">
+        <v>1</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" t="n">
         <v>0.6881588528152967</v>
-      </c>
-      <c r="H96" t="n">
-        <v>0</v>
-      </c>
-      <c r="I96" t="n">
-        <v>1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
